--- a/data/trans_orig/P36B06-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P36B06-Habitat-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de consumo de fruta fresca en 2007</t>
+          <t>Población según la frecuencia de consumo de fruta fresca (excluyendo zumos) en 2007 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8231</t>
+          <t>7980</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23301</t>
+          <t>22474</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2073</t>
+          <t>2047</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11943</t>
+          <t>11068</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12700</t>
+          <t>12242</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>29507</t>
+          <t>30311</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16762</t>
+          <t>15943</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>37209</t>
+          <t>36244</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14332</t>
+          <t>14372</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>33304</t>
+          <t>32988</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>36080</t>
+          <t>34678</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>62324</t>
+          <t>60552</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,38%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>76677</t>
+          <t>77735</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>113406</t>
+          <t>112634</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>55482</t>
+          <t>54181</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>85091</t>
+          <t>84238</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>140280</t>
+          <t>141415</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>185298</t>
+          <t>188150</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,62%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>188650</t>
+          <t>188375</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>234875</t>
+          <t>237801</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>34,31%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>150261</t>
+          <t>153100</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>196465</t>
+          <t>196907</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>356816</t>
+          <t>353492</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>416365</t>
+          <t>417612</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>30,23%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>323783</t>
+          <t>320598</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>373770</t>
+          <t>377022</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>46,72%</t>
+          <t>46,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>53,93%</t>
+          <t>54,4%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>391967</t>
+          <t>392562</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>442045</t>
+          <t>439132</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>56,94%</t>
+          <t>57,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>64,22%</t>
+          <t>63,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>731532</t>
+          <t>728654</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>801158</t>
+          <t>802235</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>52,96%</t>
+          <t>52,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>58,0%</t>
+          <t>58,07%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12571</t>
+          <t>12299</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>31262</t>
+          <t>31394</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10510</t>
+          <t>11066</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>28062</t>
+          <t>27808</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>26288</t>
+          <t>25655</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>52612</t>
+          <t>51191</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,65%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>47156</t>
+          <t>46929</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>79458</t>
+          <t>81193</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>27856</t>
+          <t>27174</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>52720</t>
+          <t>52103</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>80343</t>
+          <t>82387</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>121430</t>
+          <t>124029</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,43%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>148078</t>
+          <t>149329</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>197953</t>
+          <t>197818</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>130153</t>
+          <t>128098</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>175592</t>
+          <t>176167</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>290127</t>
+          <t>292217</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>358149</t>
+          <t>358409</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,59%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>221109</t>
+          <t>222011</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>276816</t>
+          <t>278292</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>28,97%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>203461</t>
+          <t>202116</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>256429</t>
+          <t>257276</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>26,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>442044</t>
+          <t>443437</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>519331</t>
+          <t>518099</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>26,87%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>423710</t>
+          <t>423540</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>488077</t>
+          <t>488338</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>44,1%</t>
+          <t>44,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>50,8%</t>
+          <t>50,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>499416</t>
+          <t>497693</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>564826</t>
+          <t>561854</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>51,63%</t>
+          <t>51,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>58,39%</t>
+          <t>58,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>943363</t>
+          <t>942547</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1033103</t>
+          <t>1031061</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>48,93%</t>
+          <t>48,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>53,58%</t>
+          <t>53,48%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6946</t>
+          <t>6782</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23085</t>
+          <t>22964</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10897</t>
+          <t>11093</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>28759</t>
+          <t>27890</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>21071</t>
+          <t>21448</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>45177</t>
+          <t>43938</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,23%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>26115</t>
+          <t>25158</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>49873</t>
+          <t>50731</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>14194</t>
+          <t>14888</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>31657</t>
+          <t>31877</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>45658</t>
+          <t>44429</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>75125</t>
+          <t>74504</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,47%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>83968</t>
+          <t>83598</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>121493</t>
+          <t>119334</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>63077</t>
+          <t>61639</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>95227</t>
+          <t>94688</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>156234</t>
+          <t>153788</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>206644</t>
+          <t>206505</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,16%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>175447</t>
+          <t>175607</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>224841</t>
+          <t>224401</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>25,88%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>33,14%</t>
+          <t>33,07%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>152400</t>
+          <t>152713</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>197809</t>
+          <t>197398</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>28,87%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>338602</t>
+          <t>340116</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>408510</t>
+          <t>413253</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>30,33%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>302436</t>
+          <t>302984</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>356493</t>
+          <t>357678</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>44,57%</t>
+          <t>44,65%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>52,54%</t>
+          <t>52,72%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>366421</t>
+          <t>367371</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>419032</t>
+          <t>418105</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>53,58%</t>
+          <t>53,72%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>61,28%</t>
+          <t>61,14%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>687511</t>
+          <t>679569</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>758972</t>
+          <t>757568</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>50,47%</t>
+          <t>49,88%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>55,71%</t>
+          <t>55,61%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>18711</t>
+          <t>18586</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>38360</t>
+          <t>37892</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>13673</t>
+          <t>13606</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>32244</t>
+          <t>31982</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>36775</t>
+          <t>35643</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>63391</t>
+          <t>62897</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,18%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>50278</t>
+          <t>50130</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>80972</t>
+          <t>79046</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>20112</t>
+          <t>19719</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>42536</t>
+          <t>41396</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>76440</t>
+          <t>75681</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>112131</t>
+          <t>113406</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,73%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>129370</t>
+          <t>128874</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>171947</t>
+          <t>173408</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>125363</t>
+          <t>127102</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>170911</t>
+          <t>171476</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>265618</t>
+          <t>268065</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>325615</t>
+          <t>327377</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,54%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>257121</t>
+          <t>255811</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>309752</t>
+          <t>311170</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>33,06%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>265212</t>
+          <t>264826</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>321913</t>
+          <t>323197</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>537532</t>
+          <t>539682</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>617355</t>
+          <t>615261</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>27,27%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>31,09%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>389792</t>
+          <t>388885</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>447598</t>
+          <t>449887</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>41,41%</t>
+          <t>41,31%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>47,55%</t>
+          <t>47,79%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>514689</t>
+          <t>513900</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>576575</t>
+          <t>577515</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>49,6%</t>
+          <t>49,53%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>55,57%</t>
+          <t>55,66%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>922512</t>
+          <t>920248</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1009186</t>
+          <t>1009005</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>46,62%</t>
+          <t>46,5%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>51,0%</t>
+          <t>50,99%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>59466</t>
+          <t>58330</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>93931</t>
+          <t>92086</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>48722</t>
+          <t>47929</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>80602</t>
+          <t>80331</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>116020</t>
+          <t>114936</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>160599</t>
+          <t>161032</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>160937</t>
+          <t>161648</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>214272</t>
+          <t>214246</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>93962</t>
+          <t>94777</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>133633</t>
+          <t>135217</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>266037</t>
+          <t>269552</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>332657</t>
+          <t>338832</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,09%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>476305</t>
+          <t>472696</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>558543</t>
+          <t>557305</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>408678</t>
+          <t>408221</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>488176</t>
+          <t>486088</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>905375</t>
+          <t>908929</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1021589</t>
+          <t>1021166</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,35%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>898465</t>
+          <t>892922</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>1003879</t>
+          <t>998289</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>27,28%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>30,49%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>820126</t>
+          <t>815240</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>925708</t>
+          <t>917146</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1748328</t>
+          <t>1745564</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1890419</t>
+          <t>1893657</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>28,47%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1487611</t>
+          <t>1492144</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1606903</t>
+          <t>1611346</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>45,44%</t>
+          <t>45,58%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>49,09%</t>
+          <t>49,22%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1826413</t>
+          <t>1830932</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1944171</t>
+          <t>1941798</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>54,08%</t>
+          <t>54,22%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>57,57%</t>
+          <t>57,5%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>3350941</t>
+          <t>3358261</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>3517571</t>
+          <t>3518832</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>50,38%</t>
+          <t>50,49%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>52,89%</t>
+          <t>52,91%</t>
         </is>
       </c>
     </row>
@@ -4179,7 +4179,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de consumo de fruta fresca en 2012</t>
+          <t>Población según la frecuencia de consumo de fruta fresca (excluyendo zumos) en 2012 (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4789</t>
+          <t>4872</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18070</t>
+          <t>18991</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4281</t>
+          <t>4065</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17654</t>
+          <t>17071</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12010</t>
+          <t>11070</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>30522</t>
+          <t>28950</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13051</t>
+          <t>13091</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>32003</t>
+          <t>32348</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4507,7 +4507,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7662</t>
+          <t>7370</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>23665</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>23081</t>
+          <t>24234</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>48434</t>
+          <t>49888</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,56%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>48315</t>
+          <t>49995</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>80497</t>
+          <t>78669</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>35350</t>
+          <t>34406</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>62429</t>
+          <t>61069</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>91863</t>
+          <t>91268</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>133973</t>
+          <t>133430</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,53%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>139022</t>
+          <t>139046</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>182958</t>
+          <t>182380</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>113273</t>
+          <t>116253</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>155173</t>
+          <t>161242</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>264817</t>
+          <t>263670</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>329049</t>
+          <t>326482</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,31%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>423988</t>
+          <t>425125</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>473042</t>
+          <t>473791</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>60,27%</t>
+          <t>60,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>67,24%</t>
+          <t>67,35%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>466907</t>
+          <t>465975</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>514595</t>
+          <t>515621</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>66,98%</t>
+          <t>66,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>73,82%</t>
+          <t>73,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>899942</t>
+          <t>904687</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>974735</t>
+          <t>974905</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>64,26%</t>
+          <t>64,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,6%</t>
+          <t>69,61%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13818</t>
+          <t>14085</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>33945</t>
+          <t>35226</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9002</t>
+          <t>8670</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26627</t>
+          <t>27969</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>25663</t>
+          <t>24457</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>51287</t>
+          <t>50727</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,48%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>27007</t>
+          <t>27568</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>53284</t>
+          <t>53418</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5184,82 +5184,82 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
+          <t>2,72%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>5,26%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>32975</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>22536</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>47045</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>3,2%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>2,19%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>4,56%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>71434</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>54436</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>89646</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>3,49%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
           <t>2,66%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>5,25%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>32975</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>22564</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>46920</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>3,2%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>2,19%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>4,55%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>71434</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>54732</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>90793</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>3,49%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>2,67%</t>
-        </is>
-      </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,38%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>98322</t>
+          <t>99246</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>142171</t>
+          <t>143638</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>62665</t>
+          <t>62355</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>96720</t>
+          <t>96323</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>170642</t>
+          <t>173076</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>223525</t>
+          <t>225003</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>11,0%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>218174</t>
+          <t>217416</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>276719</t>
+          <t>278006</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>175445</t>
+          <t>176488</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>230751</t>
+          <t>229779</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>408277</t>
+          <t>409860</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>486753</t>
+          <t>485477</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>23,73%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>556746</t>
+          <t>553640</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>621036</t>
+          <t>621693</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>54,85%</t>
+          <t>54,55%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>61,19%</t>
+          <t>61,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>667237</t>
+          <t>669648</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>733327</t>
+          <t>732199</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>64,71%</t>
+          <t>64,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,12%</t>
+          <t>71,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1243072</t>
+          <t>1247848</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1339650</t>
+          <t>1337509</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>60,75%</t>
+          <t>60,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>65,47%</t>
+          <t>65,37%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15091</t>
+          <t>15753</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>35337</t>
+          <t>34882</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8831</t>
+          <t>8847</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>27478</t>
+          <t>27504</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>29074</t>
+          <t>28766</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>56642</t>
+          <t>54559</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,56%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13765</t>
+          <t>13875</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>31840</t>
+          <t>32761</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18149</t>
+          <t>19162</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>42546</t>
+          <t>43697</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>38010</t>
+          <t>37482</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>68553</t>
+          <t>67416</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,4%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>61137</t>
+          <t>61133</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>95895</t>
+          <t>95995</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5984,7 +5984,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>44785</t>
+          <t>44844</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>75371</t>
+          <t>74915</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>113808</t>
+          <t>114127</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>160281</t>
+          <t>159370</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,41%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>183828</t>
+          <t>183142</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>235282</t>
+          <t>234288</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>31,01%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>162218</t>
+          <t>164149</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>212220</t>
+          <t>212385</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>27,4%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>358857</t>
+          <t>357343</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>428083</t>
+          <t>431504</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>28,19%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>395426</t>
+          <t>395540</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>452770</t>
+          <t>452343</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>52,34%</t>
+          <t>52,35%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>59,93%</t>
+          <t>59,87%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>456003</t>
+          <t>456736</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>511307</t>
+          <t>509767</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>58,84%</t>
+          <t>58,93%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>65,97%</t>
+          <t>65,77%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>864675</t>
+          <t>868496</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>947231</t>
+          <t>950891</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>56,5%</t>
+          <t>56,74%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>61,89%</t>
+          <t>62,13%</t>
         </is>
       </c>
     </row>
@@ -6420,12 +6420,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11978</t>
+          <t>12504</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>30078</t>
+          <t>30591</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6435,12 +6435,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>17438</t>
+          <t>18313</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>38205</t>
+          <t>38656</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6470,12 +6470,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>33399</t>
+          <t>33907</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>60161</t>
+          <t>61576</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,09%</t>
         </is>
       </c>
     </row>
@@ -6533,12 +6533,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>17402</t>
+          <t>18150</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>39518</t>
+          <t>40418</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6548,12 +6548,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>11620</t>
+          <t>10859</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>29909</t>
+          <t>29605</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>35258</t>
+          <t>34877</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>61773</t>
+          <t>62594</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,14%</t>
         </is>
       </c>
     </row>
@@ -6646,12 +6646,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>103426</t>
+          <t>104426</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>143695</t>
+          <t>143669</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6661,7 +6661,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>72260</t>
+          <t>70389</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>107088</t>
+          <t>105866</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>186797</t>
+          <t>187152</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>242126</t>
+          <t>240461</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,05%</t>
         </is>
       </c>
     </row>
@@ -6759,12 +6759,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>175411</t>
+          <t>175106</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>224693</t>
+          <t>223608</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6794,12 +6794,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>157673</t>
+          <t>159085</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>205464</t>
+          <t>207999</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6809,12 +6809,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>345822</t>
+          <t>339278</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>417904</t>
+          <t>411681</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6844,12 +6844,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>20,63%</t>
         </is>
       </c>
     </row>
@@ -6872,12 +6872,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>548357</t>
+          <t>549643</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>608112</t>
+          <t>610970</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>57,86%</t>
+          <t>58,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>64,16%</t>
+          <t>64,47%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6907,12 +6907,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>700096</t>
+          <t>704863</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>761901</t>
+          <t>762450</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>66,82%</t>
+          <t>67,27%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>72,71%</t>
+          <t>72,77%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6942,12 +6942,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1270236</t>
+          <t>1272158</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1355709</t>
+          <t>1358057</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>63,65%</t>
+          <t>63,75%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>67,94%</t>
+          <t>68,05%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>58191</t>
+          <t>57661</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>91744</t>
+          <t>92565</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>51335</t>
+          <t>52177</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>85938</t>
+          <t>87270</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>120702</t>
+          <t>120660</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>170266</t>
+          <t>169907</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>87577</t>
+          <t>88112</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>130401</t>
+          <t>131549</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>75576</t>
+          <t>75744</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>116741</t>
+          <t>116870</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>178859</t>
+          <t>175865</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>232531</t>
+          <t>236162</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7300,12 +7300,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,39%</t>
         </is>
       </c>
     </row>
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>347934</t>
+          <t>348573</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>421917</t>
+          <t>424449</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>236993</t>
+          <t>238944</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>304836</t>
+          <t>308392</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>605781</t>
+          <t>608532</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>709308</t>
+          <t>712586</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,22%</t>
         </is>
       </c>
     </row>
@@ -7441,12 +7441,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>762722</t>
+          <t>755637</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>866330</t>
+          <t>861011</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7456,12 +7456,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>660153</t>
+          <t>655801</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>760588</t>
+          <t>753299</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7511,12 +7511,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1448168</t>
+          <t>1445684</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1593521</t>
+          <t>1587255</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>22,76%</t>
         </is>
       </c>
     </row>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1980512</t>
+          <t>1983955</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2099905</t>
+          <t>2102060</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>57,88%</t>
+          <t>57,98%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>61,37%</t>
+          <t>61,43%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2354136</t>
+          <t>2348584</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2471592</t>
+          <t>2464574</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>66,3%</t>
+          <t>66,14%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>69,6%</t>
+          <t>69,41%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>4373026</t>
+          <t>4371137</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>4536435</t>
+          <t>4537293</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>62,72%</t>
+          <t>62,69%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>65,06%</t>
+          <t>65,07%</t>
         </is>
       </c>
     </row>
@@ -7821,7 +7821,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de consumo de fruta fresca en 2016</t>
+          <t>Población según la frecuencia de consumo de fruta fresca (excluyendo zumos) en 2016 (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8016,12 +8016,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13917</t>
+          <t>14879</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>36549</t>
+          <t>34820</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8264</t>
+          <t>8063</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23786</t>
+          <t>23491</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8066,12 +8066,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>26300</t>
+          <t>25936</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>51185</t>
+          <t>51256</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,81%</t>
         </is>
       </c>
     </row>
@@ -8129,12 +8129,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16374</t>
+          <t>16630</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>36230</t>
+          <t>37648</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8164,12 +8164,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20024</t>
+          <t>19430</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>40438</t>
+          <t>41649</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8179,12 +8179,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8199,12 +8199,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>41078</t>
+          <t>40539</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>70256</t>
+          <t>69141</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8214,12 +8214,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,13%</t>
         </is>
       </c>
     </row>
@@ -8242,12 +8242,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>64860</t>
+          <t>63692</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>98288</t>
+          <t>99453</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8257,12 +8257,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8277,12 +8277,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>62652</t>
+          <t>63625</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>95615</t>
+          <t>95369</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8292,12 +8292,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8312,12 +8312,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>135698</t>
+          <t>136069</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>185189</t>
+          <t>183300</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8327,12 +8327,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,61%</t>
         </is>
       </c>
     </row>
@@ -8355,12 +8355,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>169269</t>
+          <t>168168</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>215237</t>
+          <t>214962</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8370,12 +8370,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>31,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8390,12 +8390,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>137650</t>
+          <t>138270</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>182565</t>
+          <t>183345</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8405,12 +8405,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8425,12 +8425,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>317040</t>
+          <t>318041</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>382167</t>
+          <t>383822</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8440,12 +8440,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>28,5%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>327783</t>
+          <t>326516</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>380226</t>
+          <t>378047</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>48,65%</t>
+          <t>48,46%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>56,43%</t>
+          <t>56,11%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>364949</t>
+          <t>367344</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>416251</t>
+          <t>417581</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>54,24%</t>
+          <t>54,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>61,86%</t>
+          <t>62,06%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>708109</t>
+          <t>705400</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>780704</t>
+          <t>781216</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>52,59%</t>
+          <t>52,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>57,98%</t>
+          <t>58,01%</t>
         </is>
       </c>
     </row>
@@ -8698,12 +8698,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14034</t>
+          <t>14121</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>31959</t>
+          <t>32854</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8718,7 +8718,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8733,12 +8733,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14614</t>
+          <t>14612</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>34628</t>
+          <t>35826</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8753,7 +8753,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8768,12 +8768,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>32503</t>
+          <t>32910</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>59177</t>
+          <t>58939</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8783,12 +8783,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,86%</t>
         </is>
       </c>
     </row>
@@ -8811,12 +8811,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>26476</t>
+          <t>27615</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>51234</t>
+          <t>52282</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8826,12 +8826,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8846,12 +8846,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>27866</t>
+          <t>26695</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>52085</t>
+          <t>50958</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8861,12 +8861,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8881,12 +8881,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>60540</t>
+          <t>60479</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>94972</t>
+          <t>96138</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8901,7 +8901,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,67%</t>
         </is>
       </c>
     </row>
@@ -8924,12 +8924,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>128254</t>
+          <t>127506</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>174842</t>
+          <t>173992</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8939,12 +8939,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8959,12 +8959,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>116615</t>
+          <t>119004</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>163055</t>
+          <t>164668</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8974,12 +8974,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8994,12 +8994,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>263164</t>
+          <t>257112</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>324545</t>
+          <t>324230</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9009,12 +9009,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,75%</t>
         </is>
       </c>
     </row>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>273349</t>
+          <t>272216</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>332238</t>
+          <t>334912</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9052,12 +9052,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>32,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9072,12 +9072,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>272783</t>
+          <t>275222</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>334281</t>
+          <t>331671</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9087,12 +9087,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>26,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>31,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>560377</t>
+          <t>559226</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>646876</t>
+          <t>643400</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9122,12 +9122,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>31,25%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>474689</t>
+          <t>475111</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>538838</t>
+          <t>541186</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>46,56%</t>
+          <t>46,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>52,85%</t>
+          <t>53,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>501310</t>
+          <t>502381</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>569308</t>
+          <t>569697</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>48,24%</t>
+          <t>48,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>54,78%</t>
+          <t>54,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>996815</t>
+          <t>1001242</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1088850</t>
+          <t>1096965</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>48,42%</t>
+          <t>48,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>52,89%</t>
+          <t>53,28%</t>
         </is>
       </c>
     </row>
@@ -9380,12 +9380,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8001</t>
+          <t>7980</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23821</t>
+          <t>24634</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9400,7 +9400,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6724</t>
+          <t>7021</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21688</t>
+          <t>21513</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9430,12 +9430,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>17899</t>
+          <t>17658</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>40315</t>
+          <t>39603</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9465,12 +9465,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,57%</t>
         </is>
       </c>
     </row>
@@ -9493,12 +9493,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>21660</t>
+          <t>21269</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>44423</t>
+          <t>44641</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9508,12 +9508,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9528,12 +9528,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>13863</t>
+          <t>12883</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>32209</t>
+          <t>33357</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9543,12 +9543,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9563,12 +9563,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>41582</t>
+          <t>40619</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>71387</t>
+          <t>70154</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,54%</t>
         </is>
       </c>
     </row>
@@ -9606,12 +9606,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>100075</t>
+          <t>100965</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>146657</t>
+          <t>142536</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9621,12 +9621,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9641,12 +9641,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>71158</t>
+          <t>72757</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>108506</t>
+          <t>108508</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9656,7 +9656,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -9676,12 +9676,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>183455</t>
+          <t>181339</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>238276</t>
+          <t>236873</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9691,12 +9691,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,35%</t>
         </is>
       </c>
     </row>
@@ -9719,12 +9719,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>223040</t>
+          <t>224262</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>278113</t>
+          <t>273210</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9734,12 +9734,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>36,66%</t>
+          <t>36,02%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9754,12 +9754,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>250214</t>
+          <t>250500</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>306216</t>
+          <t>303531</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9769,12 +9769,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>31,91%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>39,01%</t>
+          <t>38,67%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9789,12 +9789,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>486491</t>
+          <t>485975</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>558673</t>
+          <t>565261</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9804,12 +9804,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>31,48%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>36,19%</t>
+          <t>36,62%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>310271</t>
+          <t>311949</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>371590</t>
+          <t>368824</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>40,9%</t>
+          <t>41,12%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>48,99%</t>
+          <t>48,62%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>355865</t>
+          <t>356679</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>412735</t>
+          <t>413452</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>45,33%</t>
+          <t>45,44%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>52,58%</t>
+          <t>52,67%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>687386</t>
+          <t>683833</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>764393</t>
+          <t>769606</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>44,53%</t>
+          <t>44,3%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>49,52%</t>
+          <t>49,86%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>18540</t>
+          <t>18256</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>40313</t>
+          <t>39956</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>14185</t>
+          <t>14306</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>32937</t>
+          <t>33696</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>35497</t>
+          <t>36839</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>64562</t>
+          <t>65057</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,29%</t>
         </is>
       </c>
     </row>
@@ -10175,12 +10175,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>23666</t>
+          <t>23638</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>46872</t>
+          <t>46002</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10195,7 +10195,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10210,12 +10210,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>17498</t>
+          <t>17073</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>37544</t>
+          <t>37960</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10225,12 +10225,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10245,12 +10245,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>46243</t>
+          <t>47306</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>78214</t>
+          <t>77241</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,91%</t>
         </is>
       </c>
     </row>
@@ -10288,12 +10288,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>89638</t>
+          <t>87895</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>127567</t>
+          <t>126405</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10303,12 +10303,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10323,12 +10323,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>77233</t>
+          <t>77323</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>116262</t>
+          <t>112663</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>176622</t>
+          <t>173322</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>228052</t>
+          <t>228025</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10373,7 +10373,7 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -10401,12 +10401,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>237725</t>
+          <t>238072</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>293195</t>
+          <t>292201</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>31,23%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10436,12 +10436,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>209914</t>
+          <t>209012</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>264852</t>
+          <t>265307</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10451,12 +10451,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>464310</t>
+          <t>463473</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>541753</t>
+          <t>539976</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10486,12 +10486,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>27,31%</t>
         </is>
       </c>
     </row>
@@ -10514,12 +10514,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>471183</t>
+          <t>471533</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>533343</t>
+          <t>534681</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10529,12 +10529,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>50,36%</t>
+          <t>50,4%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>57,0%</t>
+          <t>57,15%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10549,12 +10549,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>629621</t>
+          <t>629706</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>693629</t>
+          <t>692621</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10564,12 +10564,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>60,44%</t>
+          <t>60,45%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>66,59%</t>
+          <t>66,49%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10584,12 +10584,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1123103</t>
+          <t>1120166</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1214491</t>
+          <t>1206373</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10599,12 +10599,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>56,8%</t>
+          <t>56,65%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>61,42%</t>
+          <t>61,01%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>69759</t>
+          <t>70540</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>108838</t>
+          <t>105870</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>55098</t>
+          <t>55775</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>89922</t>
+          <t>90351</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>133683</t>
+          <t>134227</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>185176</t>
+          <t>185666</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,68%</t>
         </is>
       </c>
     </row>
@@ -10857,12 +10857,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>107292</t>
+          <t>107997</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>153532</t>
+          <t>156552</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10892,12 +10892,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>95344</t>
+          <t>96018</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>138079</t>
+          <t>137982</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10907,7 +10907,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>212984</t>
+          <t>217806</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>278835</t>
+          <t>277491</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,01%</t>
         </is>
       </c>
     </row>
@@ -10970,12 +10970,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>423352</t>
+          <t>417483</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>500898</t>
+          <t>501588</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10985,12 +10985,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11005,12 +11005,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>364035</t>
+          <t>365023</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>438545</t>
+          <t>439762</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>810743</t>
+          <t>810645</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>924780</t>
+          <t>917416</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,25%</t>
         </is>
       </c>
     </row>
@@ -11083,12 +11083,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>952365</t>
+          <t>953910</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>1054629</t>
+          <t>1060210</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11098,12 +11098,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11118,12 +11118,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>922681</t>
+          <t>922737</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>1024197</t>
+          <t>1031590</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11133,12 +11133,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11153,12 +11153,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1903675</t>
+          <t>1908835</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>2057859</t>
+          <t>2062461</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11168,12 +11168,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>27,56%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>29,78%</t>
         </is>
       </c>
     </row>
@@ -11196,12 +11196,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1648711</t>
+          <t>1643403</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1760976</t>
+          <t>1760505</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11211,12 +11211,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>48,67%</t>
+          <t>48,51%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>51,98%</t>
+          <t>51,97%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11231,12 +11231,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1918470</t>
+          <t>1917687</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2035396</t>
+          <t>2033718</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11246,12 +11246,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>54,21%</t>
+          <t>54,19%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>57,52%</t>
+          <t>57,47%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>3594942</t>
+          <t>3588996</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>3765034</t>
+          <t>3764447</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11281,12 +11281,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>51,9%</t>
+          <t>51,82%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>54,36%</t>
+          <t>54,35%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P36B06-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P36B06-Habitat-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7980</t>
+          <t>8120</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22474</t>
+          <t>24569</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2047</t>
+          <t>1925</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11068</t>
+          <t>11675</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12242</t>
+          <t>12573</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>30311</t>
+          <t>31272</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,26%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15943</t>
+          <t>15665</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>36244</t>
+          <t>35488</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14372</t>
+          <t>15022</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>32988</t>
+          <t>32262</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>34678</t>
+          <t>34046</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>60552</t>
+          <t>61399</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,44%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>77735</t>
+          <t>76055</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>112634</t>
+          <t>111939</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>54181</t>
+          <t>54953</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>84238</t>
+          <t>84489</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>141415</t>
+          <t>140438</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>188150</t>
+          <t>186185</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,48%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>188375</t>
+          <t>188176</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>237801</t>
+          <t>237256</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>27,15%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,31%</t>
+          <t>34,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>153100</t>
+          <t>153805</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>196907</t>
+          <t>199310</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>353492</t>
+          <t>353980</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>417612</t>
+          <t>420411</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>25,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,23%</t>
+          <t>30,43%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>320598</t>
+          <t>322748</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>377022</t>
+          <t>373824</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>46,26%</t>
+          <t>46,57%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>54,4%</t>
+          <t>53,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>392562</t>
+          <t>391436</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>439132</t>
+          <t>440291</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>57,03%</t>
+          <t>56,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>63,79%</t>
+          <t>63,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>728654</t>
+          <t>729334</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>802235</t>
+          <t>803646</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>52,75%</t>
+          <t>52,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>58,07%</t>
+          <t>58,18%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12299</t>
+          <t>11686</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>31394</t>
+          <t>32021</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11066</t>
+          <t>10424</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>27808</t>
+          <t>28946</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>25655</t>
+          <t>26011</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>51191</t>
+          <t>53470</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,77%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>46929</t>
+          <t>48295</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>81193</t>
+          <t>82822</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>27174</t>
+          <t>27198</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>52103</t>
+          <t>53197</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>82387</t>
+          <t>82011</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>124029</t>
+          <t>124241</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,44%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>149329</t>
+          <t>149667</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>197818</t>
+          <t>198305</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>128098</t>
+          <t>129146</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>176167</t>
+          <t>176993</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>292217</t>
+          <t>292754</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>358409</t>
+          <t>357211</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,53%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>222011</t>
+          <t>224825</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>278292</t>
+          <t>280922</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>202116</t>
+          <t>204609</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>257276</t>
+          <t>256404</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>443437</t>
+          <t>441002</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>518099</t>
+          <t>517721</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>26,85%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>423540</t>
+          <t>424327</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>488338</t>
+          <t>485703</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>44,08%</t>
+          <t>44,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>50,83%</t>
+          <t>50,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>497693</t>
+          <t>496690</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>561854</t>
+          <t>559686</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>51,45%</t>
+          <t>51,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>58,08%</t>
+          <t>57,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>942547</t>
+          <t>942539</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1031061</t>
+          <t>1029872</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>48,89%</t>
+          <t>48,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>53,48%</t>
+          <t>53,41%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6782</t>
+          <t>7014</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22964</t>
+          <t>22802</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11093</t>
+          <t>10657</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>27890</t>
+          <t>28313</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>21448</t>
+          <t>21099</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>43938</t>
+          <t>44451</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,26%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>25158</t>
+          <t>26504</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>50731</t>
+          <t>51147</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>14888</t>
+          <t>15109</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>31877</t>
+          <t>32704</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>44429</t>
+          <t>46297</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>74504</t>
+          <t>76331</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,6%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>83598</t>
+          <t>83271</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>119334</t>
+          <t>121656</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>61639</t>
+          <t>61610</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>94688</t>
+          <t>94829</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>153788</t>
+          <t>153755</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>206505</t>
+          <t>203420</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>14,93%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>175607</t>
+          <t>173347</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>224401</t>
+          <t>225950</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>33,07%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>152713</t>
+          <t>152552</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>197398</t>
+          <t>196426</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>28,72%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>340116</t>
+          <t>338197</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>413253</t>
+          <t>407972</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>29,95%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>302984</t>
+          <t>301286</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>357678</t>
+          <t>356015</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>44,65%</t>
+          <t>44,4%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>52,72%</t>
+          <t>52,47%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>367371</t>
+          <t>366936</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>418105</t>
+          <t>417469</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>53,72%</t>
+          <t>53,66%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>61,14%</t>
+          <t>61,05%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>679569</t>
+          <t>680873</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>757568</t>
+          <t>758457</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>49,88%</t>
+          <t>49,98%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>55,61%</t>
+          <t>55,67%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>18586</t>
+          <t>19083</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>37892</t>
+          <t>37731</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>13606</t>
+          <t>13562</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>31982</t>
+          <t>31711</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>35643</t>
+          <t>36826</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>62897</t>
+          <t>62555</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,16%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>50130</t>
+          <t>49812</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>79046</t>
+          <t>78449</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>19719</t>
+          <t>20707</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>41396</t>
+          <t>42655</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>75681</t>
+          <t>76006</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>113406</t>
+          <t>111571</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,64%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>128874</t>
+          <t>126805</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>173408</t>
+          <t>171073</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>127102</t>
+          <t>125799</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>171476</t>
+          <t>169405</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>268065</t>
+          <t>263888</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>327377</t>
+          <t>329538</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,65%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>255811</t>
+          <t>258286</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>311170</t>
+          <t>310053</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>32,94%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>264826</t>
+          <t>266973</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>323197</t>
+          <t>326835</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>31,5%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>539682</t>
+          <t>537430</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>615261</t>
+          <t>621277</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>31,39%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>388885</t>
+          <t>389638</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>449887</t>
+          <t>447738</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>41,31%</t>
+          <t>41,39%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>47,79%</t>
+          <t>47,56%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>513900</t>
+          <t>507697</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>577515</t>
+          <t>577672</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>49,53%</t>
+          <t>48,93%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>55,66%</t>
+          <t>55,67%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>920248</t>
+          <t>918533</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1009005</t>
+          <t>1007049</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>46,5%</t>
+          <t>46,41%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>50,99%</t>
+          <t>50,89%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>58330</t>
+          <t>59090</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>92086</t>
+          <t>94916</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>47929</t>
+          <t>48669</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>80331</t>
+          <t>80118</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>114936</t>
+          <t>113893</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>161032</t>
+          <t>162167</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,44%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>161648</t>
+          <t>160402</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>214246</t>
+          <t>214738</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>94777</t>
+          <t>92953</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>135217</t>
+          <t>135575</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>269552</t>
+          <t>269154</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>338832</t>
+          <t>336673</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,06%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>472696</t>
+          <t>475677</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>557305</t>
+          <t>560415</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>408221</t>
+          <t>404481</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>486088</t>
+          <t>482843</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>908929</t>
+          <t>907512</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1021166</t>
+          <t>1025588</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,42%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>892922</t>
+          <t>895002</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>998289</t>
+          <t>995578</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>815240</t>
+          <t>825229</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>917146</t>
+          <t>919862</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>27,24%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1745564</t>
+          <t>1740254</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1893657</t>
+          <t>1886784</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>26,17%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>28,37%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1492144</t>
+          <t>1499276</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1611346</t>
+          <t>1612942</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>45,58%</t>
+          <t>45,8%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>49,22%</t>
+          <t>49,27%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1830932</t>
+          <t>1825433</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1941798</t>
+          <t>1937002</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>54,22%</t>
+          <t>54,05%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>57,5%</t>
+          <t>57,36%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>3358261</t>
+          <t>3361931</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>3518832</t>
+          <t>3515549</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>50,49%</t>
+          <t>50,55%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>52,91%</t>
+          <t>52,86%</t>
         </is>
       </c>
     </row>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4872</t>
+          <t>5190</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18991</t>
+          <t>19056</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4065</t>
+          <t>4099</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17071</t>
+          <t>18052</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11070</t>
+          <t>11883</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>28950</t>
+          <t>30774</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13091</t>
+          <t>13361</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>32348</t>
+          <t>32203</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7370</t>
+          <t>7775</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>22505</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>24234</t>
+          <t>24297</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>49888</t>
+          <t>49571</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4577,7 +4577,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,54%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>49995</t>
+          <t>49200</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>78669</t>
+          <t>79281</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>34406</t>
+          <t>35285</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>61069</t>
+          <t>62003</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>91268</t>
+          <t>92595</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>133430</t>
+          <t>132641</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,47%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>139046</t>
+          <t>137103</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>182380</t>
+          <t>182047</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>25,88%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>116253</t>
+          <t>112627</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>161242</t>
+          <t>157182</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>263670</t>
+          <t>264986</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>326482</t>
+          <t>328345</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>23,44%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>425125</t>
+          <t>422594</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>473791</t>
+          <t>472600</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>60,43%</t>
+          <t>60,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>67,35%</t>
+          <t>67,18%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>465975</t>
+          <t>467661</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>515621</t>
+          <t>514910</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>66,85%</t>
+          <t>67,09%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>73,97%</t>
+          <t>73,87%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>904687</t>
+          <t>904176</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>974905</t>
+          <t>976232</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>64,6%</t>
+          <t>64,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,61%</t>
+          <t>69,7%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14085</t>
+          <t>13010</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>35226</t>
+          <t>32152</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8670</t>
+          <t>8527</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>27969</t>
+          <t>26134</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>24457</t>
+          <t>26676</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>50727</t>
+          <t>50825</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>27568</t>
+          <t>27814</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>53418</t>
+          <t>54216</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>22536</t>
+          <t>22096</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>47045</t>
+          <t>46513</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>54436</t>
+          <t>55064</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>89646</t>
+          <t>92492</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,52%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>99246</t>
+          <t>99863</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>143638</t>
+          <t>143178</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>62355</t>
+          <t>61155</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>96323</t>
+          <t>96442</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>173076</t>
+          <t>171743</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>225003</t>
+          <t>227071</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>217416</t>
+          <t>220241</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>278006</t>
+          <t>277693</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>176488</t>
+          <t>176745</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>229779</t>
+          <t>228755</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>409860</t>
+          <t>409967</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>485477</t>
+          <t>490305</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,96%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>553640</t>
+          <t>554548</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>621693</t>
+          <t>623232</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>54,55%</t>
+          <t>54,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>61,25%</t>
+          <t>61,4%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>669648</t>
+          <t>668798</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>732199</t>
+          <t>733862</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>64,95%</t>
+          <t>64,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,01%</t>
+          <t>71,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1247848</t>
+          <t>1249194</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1337509</t>
+          <t>1339211</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>60,99%</t>
+          <t>61,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>65,37%</t>
+          <t>65,45%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15753</t>
+          <t>15899</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>34882</t>
+          <t>34644</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8847</t>
+          <t>8902</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>27504</t>
+          <t>27895</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>28766</t>
+          <t>28131</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>54559</t>
+          <t>55796</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,65%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13875</t>
+          <t>14344</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>32761</t>
+          <t>33040</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>19162</t>
+          <t>20262</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>43697</t>
+          <t>45462</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>37482</t>
+          <t>39201</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>67416</t>
+          <t>69585</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,55%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>61133</t>
+          <t>61446</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>95995</t>
+          <t>97797</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>44844</t>
+          <t>43474</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>74915</t>
+          <t>72225</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>114127</t>
+          <t>113885</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>159370</t>
+          <t>159666</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,43%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>183142</t>
+          <t>183434</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>234288</t>
+          <t>230783</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>30,55%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>164149</t>
+          <t>162003</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>212385</t>
+          <t>211499</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>357343</t>
+          <t>360595</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>431504</t>
+          <t>432547</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>28,26%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>395540</t>
+          <t>397819</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>452343</t>
+          <t>454169</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>52,35%</t>
+          <t>52,66%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>59,87%</t>
+          <t>60,11%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>456736</t>
+          <t>456022</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>509767</t>
+          <t>510707</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>58,93%</t>
+          <t>58,84%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>65,77%</t>
+          <t>65,9%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>868496</t>
+          <t>867032</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>950891</t>
+          <t>945774</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>56,74%</t>
+          <t>56,65%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>62,13%</t>
+          <t>61,79%</t>
         </is>
       </c>
     </row>
@@ -6420,12 +6420,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>12504</t>
+          <t>12477</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>30591</t>
+          <t>30424</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6440,7 +6440,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>18313</t>
+          <t>16963</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>38656</t>
+          <t>38437</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6470,12 +6470,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>33907</t>
+          <t>33698</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>61576</t>
+          <t>60270</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,02%</t>
         </is>
       </c>
     </row>
@@ -6533,12 +6533,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>18150</t>
+          <t>18186</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>40418</t>
+          <t>38341</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6553,7 +6553,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>10859</t>
+          <t>11537</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>29605</t>
+          <t>29250</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>34877</t>
+          <t>35228</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>62594</t>
+          <t>62324</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,12%</t>
         </is>
       </c>
     </row>
@@ -6646,12 +6646,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>104426</t>
+          <t>102889</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>143669</t>
+          <t>146010</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>70389</t>
+          <t>70757</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>105866</t>
+          <t>107902</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>187152</t>
+          <t>184946</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>240461</t>
+          <t>240900</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,07%</t>
         </is>
       </c>
     </row>
@@ -6759,12 +6759,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>175106</t>
+          <t>172939</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>223608</t>
+          <t>223681</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6794,12 +6794,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>159085</t>
+          <t>156616</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>207999</t>
+          <t>208231</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6809,12 +6809,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>339278</t>
+          <t>345403</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>411681</t>
+          <t>414555</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6844,12 +6844,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,77%</t>
         </is>
       </c>
     </row>
@@ -6872,12 +6872,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>549643</t>
+          <t>549392</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>610970</t>
+          <t>613801</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>58,0%</t>
+          <t>57,97%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>64,47%</t>
+          <t>64,76%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6907,12 +6907,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>704863</t>
+          <t>701005</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>762450</t>
+          <t>764802</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>67,27%</t>
+          <t>66,9%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>72,77%</t>
+          <t>72,99%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6942,12 +6942,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1272158</t>
+          <t>1268447</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1358057</t>
+          <t>1356068</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>63,56%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>68,05%</t>
+          <t>67,95%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>57661</t>
+          <t>57583</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>92565</t>
+          <t>94431</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>52177</t>
+          <t>49959</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>87270</t>
+          <t>85494</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>120660</t>
+          <t>119256</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>169907</t>
+          <t>168141</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,41%</t>
         </is>
       </c>
     </row>
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>88112</t>
+          <t>88039</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>131549</t>
+          <t>131819</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>75744</t>
+          <t>76662</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>116870</t>
+          <t>117175</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>175865</t>
+          <t>175297</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>236162</t>
+          <t>233075</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7300,12 +7300,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,34%</t>
         </is>
       </c>
     </row>
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>348573</t>
+          <t>347727</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>424449</t>
+          <t>422058</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>238944</t>
+          <t>240312</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>308392</t>
+          <t>305079</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>608532</t>
+          <t>607835</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>712586</t>
+          <t>707878</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,15%</t>
         </is>
       </c>
     </row>
@@ -7441,12 +7441,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>755637</t>
+          <t>765691</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>861011</t>
+          <t>866663</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7456,12 +7456,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>655801</t>
+          <t>653065</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>753299</t>
+          <t>747502</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7511,12 +7511,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1445684</t>
+          <t>1445932</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1587255</t>
+          <t>1587712</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>22,77%</t>
         </is>
       </c>
     </row>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1983955</t>
+          <t>1983651</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2102060</t>
+          <t>2105002</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>57,98%</t>
+          <t>57,97%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>61,43%</t>
+          <t>61,52%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2348584</t>
+          <t>2355280</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2464574</t>
+          <t>2466220</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>66,14%</t>
+          <t>66,33%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>69,41%</t>
+          <t>69,45%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>4371137</t>
+          <t>4371169</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>4537293</t>
+          <t>4534661</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>65,07%</t>
+          <t>65,03%</t>
         </is>
       </c>
     </row>
@@ -8016,12 +8016,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14879</t>
+          <t>14253</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>34820</t>
+          <t>34155</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8063</t>
+          <t>7938</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23491</t>
+          <t>23147</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8066,12 +8066,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>25936</t>
+          <t>25759</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>51256</t>
+          <t>51846</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,85%</t>
         </is>
       </c>
     </row>
@@ -8129,12 +8129,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16630</t>
+          <t>15179</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>37648</t>
+          <t>36293</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8164,12 +8164,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19430</t>
+          <t>19422</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>41649</t>
+          <t>41147</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8184,7 +8184,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8199,12 +8199,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>40539</t>
+          <t>39933</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>69141</t>
+          <t>68031</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8214,12 +8214,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,05%</t>
         </is>
       </c>
     </row>
@@ -8242,12 +8242,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>63692</t>
+          <t>65039</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>99453</t>
+          <t>97899</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8257,12 +8257,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8277,12 +8277,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>63625</t>
+          <t>62371</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>95369</t>
+          <t>95157</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8292,12 +8292,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8312,12 +8312,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>136069</t>
+          <t>135789</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>183300</t>
+          <t>185146</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8327,12 +8327,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,75%</t>
         </is>
       </c>
     </row>
@@ -8355,12 +8355,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>168168</t>
+          <t>170453</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>214962</t>
+          <t>217894</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8370,12 +8370,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>32,34%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8390,12 +8390,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>138270</t>
+          <t>137809</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>183345</t>
+          <t>180772</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8405,12 +8405,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8425,12 +8425,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>318041</t>
+          <t>318588</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>383822</t>
+          <t>383814</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8440,7 +8440,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>326516</t>
+          <t>324563</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>378047</t>
+          <t>377319</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>48,46%</t>
+          <t>48,17%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>56,11%</t>
+          <t>56,0%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>367344</t>
+          <t>365171</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>417581</t>
+          <t>417879</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>54,6%</t>
+          <t>54,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>62,06%</t>
+          <t>62,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>705400</t>
+          <t>711160</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>781216</t>
+          <t>787786</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>52,38%</t>
+          <t>52,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>58,01%</t>
+          <t>58,5%</t>
         </is>
       </c>
     </row>
@@ -8698,12 +8698,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14121</t>
+          <t>14109</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>32854</t>
+          <t>33472</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8718,7 +8718,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8733,12 +8733,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14612</t>
+          <t>14008</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>35826</t>
+          <t>32313</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8748,12 +8748,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8768,12 +8768,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>32910</t>
+          <t>32653</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>58939</t>
+          <t>59783</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8783,12 +8783,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,9%</t>
         </is>
       </c>
     </row>
@@ -8811,12 +8811,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>27615</t>
+          <t>27486</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>52282</t>
+          <t>52313</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8826,7 +8826,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -8846,12 +8846,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26695</t>
+          <t>26241</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>50958</t>
+          <t>51970</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8861,12 +8861,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8881,12 +8881,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>60479</t>
+          <t>60719</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>96138</t>
+          <t>95139</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,62%</t>
         </is>
       </c>
     </row>
@@ -8924,12 +8924,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>127506</t>
+          <t>129194</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>173992</t>
+          <t>174350</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8939,12 +8939,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8959,12 +8959,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>119004</t>
+          <t>119930</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>164668</t>
+          <t>165132</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8974,12 +8974,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8994,12 +8994,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>257112</t>
+          <t>258220</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>324230</t>
+          <t>324921</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9009,12 +9009,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,78%</t>
         </is>
       </c>
     </row>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>272216</t>
+          <t>271010</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>334912</t>
+          <t>330539</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9052,12 +9052,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>32,42%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9072,12 +9072,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>275222</t>
+          <t>273436</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>331671</t>
+          <t>334693</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9087,12 +9087,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>32,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>559226</t>
+          <t>559569</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>643400</t>
+          <t>645674</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9122,12 +9122,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>31,36%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>475111</t>
+          <t>473256</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>541186</t>
+          <t>542665</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>46,6%</t>
+          <t>46,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>53,08%</t>
+          <t>53,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>502381</t>
+          <t>501282</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>569697</t>
+          <t>567422</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>48,34%</t>
+          <t>48,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>54,82%</t>
+          <t>54,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1001242</t>
+          <t>996883</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1096965</t>
+          <t>1085276</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>48,63%</t>
+          <t>48,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>53,28%</t>
+          <t>52,71%</t>
         </is>
       </c>
     </row>
@@ -9380,12 +9380,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7980</t>
+          <t>8188</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24634</t>
+          <t>23585</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9395,12 +9395,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7021</t>
+          <t>6925</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21513</t>
+          <t>21411</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9430,12 +9430,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>17658</t>
+          <t>18067</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>39603</t>
+          <t>38522</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9465,12 +9465,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -9493,12 +9493,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>21269</t>
+          <t>20624</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>44641</t>
+          <t>44441</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9508,12 +9508,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9528,12 +9528,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12883</t>
+          <t>13812</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>33357</t>
+          <t>34493</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9543,12 +9543,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9563,12 +9563,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>40619</t>
+          <t>39660</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>70154</t>
+          <t>70600</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,57%</t>
         </is>
       </c>
     </row>
@@ -9606,12 +9606,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>100965</t>
+          <t>101778</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>142536</t>
+          <t>145981</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9621,12 +9621,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9641,12 +9641,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>72757</t>
+          <t>70702</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>108508</t>
+          <t>107722</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9656,12 +9656,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9676,12 +9676,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>181339</t>
+          <t>182691</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>236873</t>
+          <t>241194</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9691,12 +9691,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,63%</t>
         </is>
       </c>
     </row>
@@ -9719,12 +9719,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>224262</t>
+          <t>218971</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>273210</t>
+          <t>276622</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9734,12 +9734,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>28,87%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>36,02%</t>
+          <t>36,47%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9754,12 +9754,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>250500</t>
+          <t>252375</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>303531</t>
+          <t>307105</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9769,12 +9769,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>32,15%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>38,67%</t>
+          <t>39,12%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9789,12 +9789,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>485975</t>
+          <t>489724</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>565261</t>
+          <t>562677</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9804,12 +9804,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>36,62%</t>
+          <t>36,45%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>311949</t>
+          <t>313881</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>368824</t>
+          <t>369260</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>41,12%</t>
+          <t>41,38%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>48,62%</t>
+          <t>48,68%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>356679</t>
+          <t>355965</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>413452</t>
+          <t>411175</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>45,44%</t>
+          <t>45,35%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>52,67%</t>
+          <t>52,38%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>683833</t>
+          <t>684411</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>769606</t>
+          <t>769748</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>44,3%</t>
+          <t>44,34%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>49,86%</t>
+          <t>49,87%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>18256</t>
+          <t>18494</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>39956</t>
+          <t>38360</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>14306</t>
+          <t>14488</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>33696</t>
+          <t>33340</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>36839</t>
+          <t>36064</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>65057</t>
+          <t>64572</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,27%</t>
         </is>
       </c>
     </row>
@@ -10175,12 +10175,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>23638</t>
+          <t>24396</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>46002</t>
+          <t>47547</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10190,47 +10190,47 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
+          <t>2,61%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>5,08%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>26356</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>16178</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>37507</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
           <t>2,53%</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>4,92%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>26356</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>17073</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>37960</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>2,53%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10245,12 +10245,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>47306</t>
+          <t>47488</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>77241</t>
+          <t>79323</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,01%</t>
         </is>
       </c>
     </row>
@@ -10288,12 +10288,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>87895</t>
+          <t>87937</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>126405</t>
+          <t>125164</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10303,12 +10303,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10323,12 +10323,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>77323</t>
+          <t>77618</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>112663</t>
+          <t>115344</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>173322</t>
+          <t>172989</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>228025</t>
+          <t>227395</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,5%</t>
         </is>
       </c>
     </row>
@@ -10401,12 +10401,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>238072</t>
+          <t>237395</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>292201</t>
+          <t>291906</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>31,2%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10436,12 +10436,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>209012</t>
+          <t>212063</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>265307</t>
+          <t>265703</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10451,12 +10451,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>463473</t>
+          <t>463391</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>539976</t>
+          <t>539842</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10491,7 +10491,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>27,3%</t>
         </is>
       </c>
     </row>
@@ -10514,12 +10514,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>471533</t>
+          <t>473977</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>534681</t>
+          <t>537110</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10529,12 +10529,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>50,4%</t>
+          <t>50,66%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>57,15%</t>
+          <t>57,41%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10549,12 +10549,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>629706</t>
+          <t>630424</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>692621</t>
+          <t>694272</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10564,12 +10564,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>60,45%</t>
+          <t>60,52%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>66,49%</t>
+          <t>66,65%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10584,12 +10584,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1120166</t>
+          <t>1121179</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1206373</t>
+          <t>1207238</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10599,12 +10599,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>56,65%</t>
+          <t>56,7%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>61,01%</t>
+          <t>61,06%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>70540</t>
+          <t>68928</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>105870</t>
+          <t>107830</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>55775</t>
+          <t>55799</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>90351</t>
+          <t>89174</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10799,7 +10799,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>134227</t>
+          <t>134997</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>185666</t>
+          <t>184186</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -10857,12 +10857,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>107997</t>
+          <t>107759</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>156552</t>
+          <t>153045</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10892,12 +10892,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>96018</t>
+          <t>95709</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>137982</t>
+          <t>137597</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>217806</t>
+          <t>216244</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>277491</t>
+          <t>278030</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10942,7 +10942,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -10970,12 +10970,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>417483</t>
+          <t>419102</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>501588</t>
+          <t>501793</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10985,7 +10985,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -11005,12 +11005,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>365023</t>
+          <t>364202</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>439762</t>
+          <t>442749</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>810645</t>
+          <t>807597</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>917416</t>
+          <t>920882</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,3%</t>
         </is>
       </c>
     </row>
@@ -11083,12 +11083,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>953910</t>
+          <t>954862</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>1060210</t>
+          <t>1061342</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11098,12 +11098,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11118,12 +11118,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>922737</t>
+          <t>921098</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>1031590</t>
+          <t>1029463</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11133,12 +11133,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11153,12 +11153,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1908835</t>
+          <t>1909679</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>2062461</t>
+          <t>2058691</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11168,12 +11168,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>29,72%</t>
         </is>
       </c>
     </row>
@@ -11196,12 +11196,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1643403</t>
+          <t>1646863</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1760505</t>
+          <t>1766529</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11211,12 +11211,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>48,51%</t>
+          <t>48,62%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>51,97%</t>
+          <t>52,15%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11231,12 +11231,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1917687</t>
+          <t>1914703</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2033718</t>
+          <t>2038008</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11246,12 +11246,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>54,19%</t>
+          <t>54,11%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>57,47%</t>
+          <t>57,59%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>3588996</t>
+          <t>3595894</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>3764447</t>
+          <t>3756052</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11281,12 +11281,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>51,82%</t>
+          <t>51,92%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>54,35%</t>
+          <t>54,23%</t>
         </is>
       </c>
     </row>
